--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/111.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/111.xlsx
@@ -426,13 +426,13 @@
         <v>-17.23348372096389</v>
       </c>
       <c r="E2">
-        <v>-20.74739062077782</v>
+        <v>-13.12371438080931</v>
       </c>
       <c r="F2">
-        <v>-4.290591237602757</v>
+        <v>-2.469743595630719</v>
       </c>
       <c r="G2">
-        <v>-15.22714900828702</v>
+        <v>-12.89944568127469</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-17.06158736475512</v>
       </c>
       <c r="E3">
-        <v>-20.88589606524953</v>
+        <v>-12.90832468829237</v>
       </c>
       <c r="F3">
-        <v>-4.202417326146569</v>
+        <v>-2.282472920145029</v>
       </c>
       <c r="G3">
-        <v>-15.10051745263966</v>
+        <v>-12.7548130416716</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-16.88225877888463</v>
       </c>
       <c r="E4">
-        <v>-23.03609247912844</v>
+        <v>-14.46552974242359</v>
       </c>
       <c r="F4">
-        <v>-4.204753322222464</v>
+        <v>-2.189815055937488</v>
       </c>
       <c r="G4">
-        <v>-14.50580941536849</v>
+        <v>-12.67068310259527</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-16.70026606271749</v>
       </c>
       <c r="E5">
-        <v>-22.03565862878109</v>
+        <v>-15.29679914229934</v>
       </c>
       <c r="F5">
-        <v>-3.941121254444507</v>
+        <v>-2.209339675621472</v>
       </c>
       <c r="G5">
-        <v>-15.41673475363219</v>
+        <v>-12.80670550653687</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-16.5223112527854</v>
       </c>
       <c r="E6">
-        <v>-23.67561641855951</v>
+        <v>-15.59532366590537</v>
       </c>
       <c r="F6">
-        <v>-3.53782809928936</v>
+        <v>-1.96233542671991</v>
       </c>
       <c r="G6">
-        <v>-14.8992368768986</v>
+        <v>-12.71840229223164</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-16.34817301845878</v>
       </c>
       <c r="E7">
-        <v>-22.61955860893874</v>
+        <v>-16.64064542425147</v>
       </c>
       <c r="F7">
-        <v>-3.721698326586557</v>
+        <v>-1.973582170947719</v>
       </c>
       <c r="G7">
-        <v>-15.58021044232163</v>
+        <v>-12.68652118465726</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-16.1898655800553</v>
       </c>
       <c r="E8">
-        <v>-24.50063938860273</v>
+        <v>-16.2364798173871</v>
       </c>
       <c r="F8">
-        <v>-3.481776618978931</v>
+        <v>-1.381512368368592</v>
       </c>
       <c r="G8">
-        <v>-14.01837948409075</v>
+        <v>-12.17934097054775</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-16.04787495042789</v>
       </c>
       <c r="E9">
-        <v>-26.08577063568209</v>
+        <v>-17.42235455338804</v>
       </c>
       <c r="F9">
-        <v>-3.342379780803233</v>
+        <v>-1.318428048808395</v>
       </c>
       <c r="G9">
-        <v>-14.54709573033235</v>
+        <v>-12.00285855230538</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-15.93102580413896</v>
       </c>
       <c r="E10">
-        <v>-25.23203236253901</v>
+        <v>-17.85116531625394</v>
       </c>
       <c r="F10">
-        <v>-3.901656174640333</v>
+        <v>-1.334035319044541</v>
       </c>
       <c r="G10">
-        <v>-14.05531629856582</v>
+        <v>-11.73531988958646</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-15.83719940270489</v>
       </c>
       <c r="E11">
-        <v>-24.86025765079698</v>
+        <v>-18.41734354368854</v>
       </c>
       <c r="F11">
-        <v>-3.307929637255607</v>
+        <v>-0.9806131950075345</v>
       </c>
       <c r="G11">
-        <v>-13.49398271477514</v>
+        <v>-10.95819129550043</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-15.7717879253726</v>
       </c>
       <c r="E12">
-        <v>-26.12756024803252</v>
+        <v>-19.50172210133332</v>
       </c>
       <c r="F12">
-        <v>-2.895063040026305</v>
+        <v>-0.4886954965290761</v>
       </c>
       <c r="G12">
-        <v>-14.85495864863332</v>
+        <v>-10.82889939111472</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-15.73161447882171</v>
       </c>
       <c r="E13">
-        <v>-26.95654122846829</v>
+        <v>-20.38863207332781</v>
       </c>
       <c r="F13">
-        <v>-2.095502942026556</v>
+        <v>-0.2995411135694202</v>
       </c>
       <c r="G13">
-        <v>-12.48076057119785</v>
+        <v>-10.3919364581555</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-15.7147028064654</v>
       </c>
       <c r="E14">
-        <v>-27.30453049895302</v>
+        <v>-21.65861349186786</v>
       </c>
       <c r="F14">
-        <v>-2.462294087577343</v>
+        <v>-0.07940827484727116</v>
       </c>
       <c r="G14">
-        <v>-13.15598788777585</v>
+        <v>-10.36260343730205</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-15.70959741442663</v>
       </c>
       <c r="E15">
-        <v>-30.09397674031557</v>
+        <v>-21.67916358150311</v>
       </c>
       <c r="F15">
-        <v>-2.013822602640913</v>
+        <v>-0.05044275187358085</v>
       </c>
       <c r="G15">
-        <v>-13.0625193152971</v>
+        <v>-9.958551550658399</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-15.69798503148344</v>
       </c>
       <c r="E16">
-        <v>-30.19297268545418</v>
+        <v>-22.7113362727948</v>
       </c>
       <c r="F16">
-        <v>-1.758614202982025</v>
+        <v>0.3853687940458643</v>
       </c>
       <c r="G16">
-        <v>-12.94057535156309</v>
+        <v>-9.019159958745494</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-15.65756147472296</v>
       </c>
       <c r="E17">
-        <v>-29.2290164901728</v>
+        <v>-24.18365799386916</v>
       </c>
       <c r="F17">
-        <v>-1.967558283194561</v>
+        <v>0.5441643400603211</v>
       </c>
       <c r="G17">
-        <v>-12.86740792902484</v>
+        <v>-8.976395962343059</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-15.56174937770391</v>
       </c>
       <c r="E18">
-        <v>-29.79286268944851</v>
+        <v>-24.52448712802989</v>
       </c>
       <c r="F18">
-        <v>-1.542868398025102</v>
+        <v>0.7458544069265419</v>
       </c>
       <c r="G18">
-        <v>-11.31566488789402</v>
+        <v>-9.438284979285935</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-15.39344582328336</v>
       </c>
       <c r="E19">
-        <v>-32.37502630680019</v>
+        <v>-25.70951460892057</v>
       </c>
       <c r="F19">
-        <v>-1.456407550357903</v>
+        <v>1.395408765422941</v>
       </c>
       <c r="G19">
-        <v>-11.4204627865259</v>
+        <v>-8.44546058319901</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-15.13687592537836</v>
       </c>
       <c r="E20">
-        <v>-31.90424942010256</v>
+        <v>-26.58010246040848</v>
       </c>
       <c r="F20">
-        <v>-0.5176693031767944</v>
+        <v>1.753656129581254</v>
       </c>
       <c r="G20">
-        <v>-11.4306577441542</v>
+        <v>-8.328691115244581</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-14.7932926598349</v>
       </c>
       <c r="E21">
-        <v>-32.20660112794442</v>
+        <v>-27.30866294422123</v>
       </c>
       <c r="F21">
-        <v>-0.5273976499552718</v>
+        <v>2.182725593209314</v>
       </c>
       <c r="G21">
-        <v>-11.94868299129519</v>
+        <v>-7.720289722593019</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-14.36294314079018</v>
       </c>
       <c r="E22">
-        <v>-32.75617689310801</v>
+        <v>-28.06250817857953</v>
       </c>
       <c r="F22">
-        <v>-0.7356740660411515</v>
+        <v>2.424832534025525</v>
       </c>
       <c r="G22">
-        <v>-11.50581194332628</v>
+        <v>-8.408656916698085</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-13.86269982050952</v>
       </c>
       <c r="E23">
-        <v>-34.28962765506687</v>
+        <v>-28.00778131295227</v>
       </c>
       <c r="F23">
-        <v>-0.4180432123769035</v>
+        <v>2.462137231643198</v>
       </c>
       <c r="G23">
-        <v>-11.36212047714829</v>
+        <v>-8.158276067431958</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-13.30306870497796</v>
       </c>
       <c r="E24">
-        <v>-33.22506822186417</v>
+        <v>-28.1586114120304</v>
       </c>
       <c r="F24">
-        <v>-0.1626583704612187</v>
+        <v>2.154465010895406</v>
       </c>
       <c r="G24">
-        <v>-10.0647253116898</v>
+        <v>-8.127137716693749</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-12.71211527394947</v>
       </c>
       <c r="E25">
-        <v>-35.71425389728691</v>
+        <v>-28.1709983648067</v>
       </c>
       <c r="F25">
-        <v>-0.5616456718566145</v>
+        <v>2.64038367264279</v>
       </c>
       <c r="G25">
-        <v>-11.70629885271164</v>
+        <v>-7.524166672791702</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-12.1102104914641</v>
       </c>
       <c r="E26">
-        <v>-34.57637990117267</v>
+        <v>-29.01649251347</v>
       </c>
       <c r="F26">
-        <v>-0.3398560983288665</v>
+        <v>2.189176918542317</v>
       </c>
       <c r="G26">
-        <v>-11.40903164133371</v>
+        <v>-7.634847884359655</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-11.5337384954598</v>
       </c>
       <c r="E27">
-        <v>-35.07542146754142</v>
+        <v>-28.35671128580207</v>
       </c>
       <c r="F27">
-        <v>-0.8730969046959782</v>
+        <v>2.275655161924974</v>
       </c>
       <c r="G27">
-        <v>-11.33667354961871</v>
+        <v>-7.799829972678173</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-11.00547861759628</v>
       </c>
       <c r="E28">
-        <v>-34.83792838435375</v>
+        <v>-28.3376210499475</v>
       </c>
       <c r="F28">
-        <v>-0.5754951464640194</v>
+        <v>2.03167445404363</v>
       </c>
       <c r="G28">
-        <v>-10.84590969749812</v>
+        <v>-7.405646700588933</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-10.55836322101426</v>
       </c>
       <c r="E29">
-        <v>-34.26834452363278</v>
+        <v>-28.94056973384647</v>
       </c>
       <c r="F29">
-        <v>-1.282634293333429</v>
+        <v>1.946417224212699</v>
       </c>
       <c r="G29">
-        <v>-10.61263705753756</v>
+        <v>-7.57242367581384</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-10.20671346033368</v>
       </c>
       <c r="E30">
-        <v>-33.08795617979194</v>
+        <v>-28.90562876697069</v>
       </c>
       <c r="F30">
-        <v>-0.6928656953992787</v>
+        <v>1.730281258209058</v>
       </c>
       <c r="G30">
-        <v>-11.64186959231985</v>
+        <v>-6.973693786500057</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-9.968198831468609</v>
       </c>
       <c r="E31">
-        <v>-32.8360244574335</v>
+        <v>-28.77126407418984</v>
       </c>
       <c r="F31">
-        <v>-0.80186890519886</v>
+        <v>1.740193502550957</v>
       </c>
       <c r="G31">
-        <v>-10.47131875819289</v>
+        <v>-7.453425937350897</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-9.841544694462781</v>
       </c>
       <c r="E32">
-        <v>-33.20569764424517</v>
+        <v>-27.48090492428452</v>
       </c>
       <c r="F32">
-        <v>-0.8438638190511837</v>
+        <v>1.342539044306665</v>
       </c>
       <c r="G32">
-        <v>-11.24944465671273</v>
+        <v>-7.585882064181029</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-9.823565115165696</v>
       </c>
       <c r="E33">
-        <v>-33.8132065541788</v>
+        <v>-27.61259910218351</v>
       </c>
       <c r="F33">
-        <v>-0.827084408940077</v>
+        <v>1.542783610055001</v>
       </c>
       <c r="G33">
-        <v>-11.80833197282153</v>
+        <v>-7.502993534157774</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-9.900828672288609</v>
       </c>
       <c r="E34">
-        <v>-33.63112561648699</v>
+        <v>-28.30311409365516</v>
       </c>
       <c r="F34">
-        <v>-0.08714191291980734</v>
+        <v>1.719939919552508</v>
       </c>
       <c r="G34">
-        <v>-11.31627710750064</v>
+        <v>-7.356308849306074</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-10.05633822558953</v>
       </c>
       <c r="E35">
-        <v>-32.75482086961046</v>
+        <v>-26.59805263975439</v>
       </c>
       <c r="F35">
-        <v>-0.9401888657509186</v>
+        <v>1.507069377850703</v>
       </c>
       <c r="G35">
-        <v>-11.82035314629131</v>
+        <v>-7.599330009569854</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-10.27399517606044</v>
       </c>
       <c r="E36">
-        <v>-30.93969931560173</v>
+        <v>-25.38668133943033</v>
       </c>
       <c r="F36">
-        <v>-0.806306469375657</v>
+        <v>1.540967828708064</v>
       </c>
       <c r="G36">
-        <v>-10.83782552687174</v>
+        <v>-7.860245213261125</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-10.53278665399446</v>
       </c>
       <c r="E37">
-        <v>-31.20099237628633</v>
+        <v>-25.58993119524478</v>
       </c>
       <c r="F37">
-        <v>-0.1644567560926964</v>
+        <v>1.84076724565965</v>
       </c>
       <c r="G37">
-        <v>-11.67489159528055</v>
+        <v>-7.974551443693838</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-10.82249404994771</v>
       </c>
       <c r="E38">
-        <v>-32.10342082239604</v>
+        <v>-25.75979753843027</v>
       </c>
       <c r="F38">
-        <v>-0.977136537017985</v>
+        <v>1.747668689993819</v>
       </c>
       <c r="G38">
-        <v>-10.47833252353692</v>
+        <v>-8.418281426633225</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-11.1277441980292</v>
       </c>
       <c r="E39">
-        <v>-31.1171411162437</v>
+        <v>-24.71370743598908</v>
       </c>
       <c r="F39">
-        <v>-0.610413317594227</v>
+        <v>1.666180531845626</v>
       </c>
       <c r="G39">
-        <v>-12.28026582957872</v>
+        <v>-7.519501272207383</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-11.44780644502657</v>
       </c>
       <c r="E40">
-        <v>-28.51593294836203</v>
+        <v>-24.56594448347433</v>
       </c>
       <c r="F40">
-        <v>-0.6287061549502485</v>
+        <v>1.909990596041994</v>
       </c>
       <c r="G40">
-        <v>-11.73624931466089</v>
+        <v>-8.464209645480089</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-11.77243120774482</v>
       </c>
       <c r="E41">
-        <v>-30.47736590752748</v>
+        <v>-24.90430245689679</v>
       </c>
       <c r="F41">
-        <v>-0.8466380214831593</v>
+        <v>2.228416682412929</v>
       </c>
       <c r="G41">
-        <v>-11.97147087545872</v>
+        <v>-8.413762227746007</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-12.10309523707347</v>
       </c>
       <c r="E42">
-        <v>-28.75440826602802</v>
+        <v>-23.65011154781374</v>
       </c>
       <c r="F42">
-        <v>-0.09942328803371281</v>
+        <v>2.05638796713875</v>
       </c>
       <c r="G42">
-        <v>-10.98612887336993</v>
+        <v>-8.833545155923408</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-12.42842816791618</v>
       </c>
       <c r="E43">
-        <v>-30.17580746304866</v>
+        <v>-22.67389507270147</v>
       </c>
       <c r="F43">
-        <v>-0.7761174477480317</v>
+        <v>2.030420305795791</v>
       </c>
       <c r="G43">
-        <v>-12.8673609356222</v>
+        <v>-8.693091013038401</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-12.74841911079667</v>
       </c>
       <c r="E44">
-        <v>-29.51002484501636</v>
+        <v>-22.73902988590875</v>
       </c>
       <c r="F44">
-        <v>-0.3387369739676844</v>
+        <v>1.90393854379714</v>
       </c>
       <c r="G44">
-        <v>-12.05202278907293</v>
+        <v>-8.805756390495599</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-13.05324685488085</v>
       </c>
       <c r="E45">
-        <v>-30.34150398206402</v>
+        <v>-21.5230609806481</v>
       </c>
       <c r="F45">
-        <v>-0.7785586464840819</v>
+        <v>2.078308225351631</v>
       </c>
       <c r="G45">
-        <v>-11.71718957377347</v>
+        <v>-9.075588592337818</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-13.34294099094721</v>
       </c>
       <c r="E46">
-        <v>-28.21733366695215</v>
+        <v>-21.55364938205546</v>
       </c>
       <c r="F46">
-        <v>-0.7054038644080519</v>
+        <v>2.02407004128593</v>
       </c>
       <c r="G46">
-        <v>-12.36947758300165</v>
+        <v>-8.969459213964472</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-13.60932120027845</v>
       </c>
       <c r="E47">
-        <v>-27.36857717079321</v>
+        <v>-20.25443350899995</v>
       </c>
       <c r="F47">
-        <v>-0.8047789598848947</v>
+        <v>2.319129539958698</v>
       </c>
       <c r="G47">
-        <v>-12.29790271466398</v>
+        <v>-8.733937417538664</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-13.85145068707579</v>
       </c>
       <c r="E48">
-        <v>-26.88578296712719</v>
+        <v>-20.42012587480399</v>
       </c>
       <c r="F48">
-        <v>-0.2555175279476404</v>
+        <v>2.091646597271508</v>
       </c>
       <c r="G48">
-        <v>-11.34832791347344</v>
+        <v>-8.811633176570195</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-14.06303011698696</v>
       </c>
       <c r="E49">
-        <v>-26.28874222633779</v>
+        <v>-19.32049672517443</v>
       </c>
       <c r="F49">
-        <v>-1.009577889613822</v>
+        <v>1.978786508844492</v>
       </c>
       <c r="G49">
-        <v>-11.27562389810012</v>
+        <v>-9.244942372474153</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-14.24337627667797</v>
       </c>
       <c r="E50">
-        <v>-25.86772288791727</v>
+        <v>-19.74120457274559</v>
       </c>
       <c r="F50">
-        <v>-0.8726528997680777</v>
+        <v>1.79584985161025</v>
       </c>
       <c r="G50">
-        <v>-12.07286697388838</v>
+        <v>-9.541485102228052</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-14.39068150615572</v>
       </c>
       <c r="E51">
-        <v>-25.68878177798703</v>
+        <v>-18.25518140751061</v>
       </c>
       <c r="F51">
-        <v>-0.7472886053958033</v>
+        <v>2.105122478180251</v>
       </c>
       <c r="G51">
-        <v>-11.77630466355005</v>
+        <v>-9.327508475540407</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-14.50637540510592</v>
       </c>
       <c r="E52">
-        <v>-25.81732366849047</v>
+        <v>-18.39131536831584</v>
       </c>
       <c r="F52">
-        <v>-0.9649056923156503</v>
+        <v>2.142392384367006</v>
       </c>
       <c r="G52">
-        <v>-12.169691658539</v>
+        <v>-9.085156971264247</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-14.59394207001935</v>
       </c>
       <c r="E53">
-        <v>-25.74684782551946</v>
+        <v>-17.96245476691405</v>
       </c>
       <c r="F53">
-        <v>-0.8898522921524039</v>
+        <v>1.921610933968465</v>
       </c>
       <c r="G53">
-        <v>-12.07246622459364</v>
+        <v>-9.298321656384056</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-14.65550077492175</v>
       </c>
       <c r="E54">
-        <v>-25.56626619711591</v>
+        <v>-18.08241196960907</v>
       </c>
       <c r="F54">
-        <v>-1.749326547661836</v>
+        <v>2.036918019703351</v>
       </c>
       <c r="G54">
-        <v>-11.60385323495636</v>
+        <v>-9.287936114400607</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-14.69770507521544</v>
       </c>
       <c r="E55">
-        <v>-24.89704679671231</v>
+        <v>-18.82969097686282</v>
       </c>
       <c r="F55">
-        <v>-0.7351977547845417</v>
+        <v>2.063687540692219</v>
       </c>
       <c r="G55">
-        <v>-11.24787820995806</v>
+        <v>-9.568455399226547</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-14.71985848301094</v>
       </c>
       <c r="E56">
-        <v>-24.4533966097828</v>
+        <v>-16.28822883049446</v>
       </c>
       <c r="F56">
-        <v>-0.8563025839716211</v>
+        <v>2.064607028509327</v>
       </c>
       <c r="G56">
-        <v>-11.70378862178729</v>
+        <v>-9.581532618883434</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-14.72773250821383</v>
       </c>
       <c r="E57">
-        <v>-23.95927659883398</v>
+        <v>-16.55076577797085</v>
       </c>
       <c r="F57">
-        <v>-1.132094256855272</v>
+        <v>1.779497879078987</v>
       </c>
       <c r="G57">
-        <v>-12.65666993100247</v>
+        <v>-9.731428519582204</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-14.71808934158337</v>
       </c>
       <c r="E58">
-        <v>-23.40758061928905</v>
+        <v>-16.32163726239138</v>
       </c>
       <c r="F58">
-        <v>-0.9209873093540261</v>
+        <v>2.044277235709822</v>
       </c>
       <c r="G58">
-        <v>-12.98999544130057</v>
+        <v>-10.0922804154767</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-14.69615653498294</v>
       </c>
       <c r="E59">
-        <v>-23.13878062913482</v>
+        <v>-15.89790587697575</v>
       </c>
       <c r="F59">
-        <v>-1.47341476150478</v>
+        <v>1.886978549592223</v>
       </c>
       <c r="G59">
-        <v>-12.06474233672084</v>
+        <v>-10.17773530743302</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-14.65664405000896</v>
       </c>
       <c r="E60">
-        <v>-22.91818280961656</v>
+        <v>-15.4067927910261</v>
       </c>
       <c r="F60">
-        <v>-1.19622066260819</v>
+        <v>2.230910068295356</v>
       </c>
       <c r="G60">
-        <v>-12.64898259355394</v>
+        <v>-10.11926768231504</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-14.6061839798197</v>
       </c>
       <c r="E61">
-        <v>-23.80269637867662</v>
+        <v>-15.55991338614988</v>
       </c>
       <c r="F61">
-        <v>-0.5006471814166673</v>
+        <v>2.07204079758205</v>
       </c>
       <c r="G61">
-        <v>-12.5652090211143</v>
+        <v>-10.0730953588489</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-14.54129781545055</v>
       </c>
       <c r="E62">
-        <v>-22.60500160324521</v>
+        <v>-15.35698748081876</v>
       </c>
       <c r="F62">
-        <v>-1.142920190442458</v>
+        <v>2.017728060450097</v>
       </c>
       <c r="G62">
-        <v>-11.83134699176449</v>
+        <v>-10.63195265139491</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-14.47074751951962</v>
       </c>
       <c r="E63">
-        <v>-23.09177458336042</v>
+        <v>-14.69810542340266</v>
       </c>
       <c r="F63">
-        <v>-1.283856963619961</v>
+        <v>2.33660312195335</v>
       </c>
       <c r="G63">
-        <v>-13.01083701537142</v>
+        <v>-10.82269626196624</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-14.38993723052456</v>
       </c>
       <c r="E64">
-        <v>-23.75783754315714</v>
+        <v>-14.88053523084575</v>
       </c>
       <c r="F64">
-        <v>-0.7435775194312616</v>
+        <v>1.897169125381463</v>
       </c>
       <c r="G64">
-        <v>-13.44039065518107</v>
+        <v>-10.88294180415077</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-14.30620145312345</v>
       </c>
       <c r="E65">
-        <v>-23.9399101744263</v>
+        <v>-14.08942323126976</v>
       </c>
       <c r="F65">
-        <v>-0.964382164117081</v>
+        <v>1.964472320124117</v>
       </c>
       <c r="G65">
-        <v>-12.61019737190836</v>
+        <v>-11.01036441540923</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-14.21355571696823</v>
       </c>
       <c r="E66">
-        <v>-24.12957902920857</v>
+        <v>-14.60205825830467</v>
       </c>
       <c r="F66">
-        <v>-1.056786547899366</v>
+        <v>1.511943491648775</v>
       </c>
       <c r="G66">
-        <v>-12.83885029931495</v>
+        <v>-11.06176214417448</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-14.11748531877702</v>
       </c>
       <c r="E67">
-        <v>-21.64140258413777</v>
+        <v>-13.26504816219322</v>
       </c>
       <c r="F67">
-        <v>-1.183664269516555</v>
+        <v>1.695355631772225</v>
       </c>
       <c r="G67">
-        <v>-12.31241584384598</v>
+        <v>-10.95309251131398</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-14.00985686784073</v>
       </c>
       <c r="E68">
-        <v>-22.79256477988579</v>
+        <v>-14.43739173569787</v>
       </c>
       <c r="F68">
-        <v>-1.339580410438881</v>
+        <v>1.800520187027233</v>
       </c>
       <c r="G68">
-        <v>-12.87465535600977</v>
+        <v>-10.88852357608657</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-13.89369932938306</v>
       </c>
       <c r="E69">
-        <v>-22.48469137758758</v>
+        <v>-14.14158756550961</v>
       </c>
       <c r="F69">
-        <v>-1.396379078146634</v>
+        <v>1.874945684699158</v>
       </c>
       <c r="G69">
-        <v>-13.11226183199158</v>
+        <v>-11.27632488302283</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-13.76228236094665</v>
       </c>
       <c r="E70">
-        <v>-21.87345911370124</v>
+        <v>-14.44388320499858</v>
       </c>
       <c r="F70">
-        <v>-1.11273613901925</v>
+        <v>2.016256879942725</v>
       </c>
       <c r="G70">
-        <v>-13.3823877426003</v>
+        <v>-10.90058129998062</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-13.61997539855376</v>
       </c>
       <c r="E71">
-        <v>-23.51397758700851</v>
+        <v>-14.8147026781359</v>
       </c>
       <c r="F71">
-        <v>-0.9864134235619366</v>
+        <v>1.717267606311077</v>
       </c>
       <c r="G71">
-        <v>-13.45337388803267</v>
+        <v>-10.78439011195313</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-13.46497557192509</v>
       </c>
       <c r="E72">
-        <v>-21.89143005910377</v>
+        <v>-13.36802703699234</v>
       </c>
       <c r="F72">
-        <v>-1.198994865040165</v>
+        <v>1.803977792566518</v>
       </c>
       <c r="G72">
-        <v>-12.47546075967789</v>
+        <v>-10.71133103531541</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-13.30424327611374</v>
       </c>
       <c r="E73">
-        <v>-22.86271251916215</v>
+        <v>-14.25639063295052</v>
       </c>
       <c r="F73">
-        <v>-1.277152157861702</v>
+        <v>1.879476854392471</v>
       </c>
       <c r="G73">
-        <v>-13.27406664414272</v>
+        <v>-10.67200408416718</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-13.14265046267297</v>
       </c>
       <c r="E74">
-        <v>-22.62211698711483</v>
+        <v>-13.72178511800727</v>
       </c>
       <c r="F74">
-        <v>-1.359103373388059</v>
+        <v>1.752546117261503</v>
       </c>
       <c r="G74">
-        <v>-12.05605377872161</v>
+        <v>-10.75467070090019</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-12.98902236683586</v>
       </c>
       <c r="E75">
-        <v>-21.69006576123078</v>
+        <v>-15.14091250843323</v>
       </c>
       <c r="F75">
-        <v>-1.723047420175425</v>
+        <v>1.764216157232142</v>
       </c>
       <c r="G75">
-        <v>-12.33976861492707</v>
+        <v>-10.39973083613227</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-12.85379764247571</v>
       </c>
       <c r="E76">
-        <v>-22.4884251145686</v>
+        <v>-14.68533845179014</v>
       </c>
       <c r="F76">
-        <v>-1.642787730885584</v>
+        <v>1.837975647512216</v>
       </c>
       <c r="G76">
-        <v>-13.0308509834069</v>
+        <v>-10.71926900424469</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-12.74358208233391</v>
       </c>
       <c r="E77">
-        <v>-22.94395763909844</v>
+        <v>-14.58326913027115</v>
       </c>
       <c r="F77">
-        <v>-1.872719327615448</v>
+        <v>1.511343753649148</v>
       </c>
       <c r="G77">
-        <v>-13.45405398699866</v>
+        <v>-10.87387468818583</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-12.66745917059338</v>
       </c>
       <c r="E78">
-        <v>-23.51727523680043</v>
+        <v>-15.09918104104135</v>
       </c>
       <c r="F78">
-        <v>-2.377670558809554</v>
+        <v>1.490162399159565</v>
       </c>
       <c r="G78">
-        <v>-12.84868105807279</v>
+        <v>-10.16732626874825</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-12.62375736009355</v>
       </c>
       <c r="E79">
-        <v>-23.40907162215467</v>
+        <v>-15.0374643207544</v>
       </c>
       <c r="F79">
-        <v>-0.9504291435843261</v>
+        <v>1.528048610694003</v>
       </c>
       <c r="G79">
-        <v>-13.13568021097387</v>
+        <v>-10.62953118578665</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-12.61653976518623</v>
       </c>
       <c r="E80">
-        <v>-22.93073796745151</v>
+        <v>-15.53955434423557</v>
       </c>
       <c r="F80">
-        <v>-1.451516869211775</v>
+        <v>1.813505674433518</v>
       </c>
       <c r="G80">
-        <v>-12.10372989107223</v>
+        <v>-9.901607295009331</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-12.63733736083575</v>
       </c>
       <c r="E81">
-        <v>-23.62228503193739</v>
+        <v>-15.89319198212207</v>
       </c>
       <c r="F81">
-        <v>-1.911132380818067</v>
+        <v>1.625622007069757</v>
       </c>
       <c r="G81">
-        <v>-12.51872210292493</v>
+        <v>-9.658035267636826</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-12.68712123231022</v>
       </c>
       <c r="E82">
-        <v>-24.65404655530792</v>
+        <v>-16.99147964449371</v>
       </c>
       <c r="F82">
-        <v>-1.342330590216175</v>
+        <v>1.589432291976252</v>
       </c>
       <c r="G82">
-        <v>-12.23076219601432</v>
+        <v>-9.700194876666419</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-12.75460686791634</v>
       </c>
       <c r="E83">
-        <v>-24.82828623001845</v>
+        <v>-17.46191389125704</v>
       </c>
       <c r="F83">
-        <v>-1.606236847604458</v>
+        <v>1.467766658057478</v>
       </c>
       <c r="G83">
-        <v>-11.75159918748434</v>
+        <v>-9.398061237370653</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-12.83939433094486</v>
       </c>
       <c r="E84">
-        <v>-25.60857911409326</v>
+        <v>-17.53984474855612</v>
       </c>
       <c r="F84">
-        <v>-1.644102349953827</v>
+        <v>1.438308256479121</v>
       </c>
       <c r="G84">
-        <v>-11.66520442747522</v>
+        <v>-9.163902249621406</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-12.9276142923984</v>
       </c>
       <c r="E85">
-        <v>-24.79832911673246</v>
+        <v>-19.57069863501608</v>
       </c>
       <c r="F85">
-        <v>-1.165780645657516</v>
+        <v>1.356468870552141</v>
       </c>
       <c r="G85">
-        <v>-11.78483527150151</v>
+        <v>-9.583599023227301</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-13.01630001190268</v>
       </c>
       <c r="E86">
-        <v>-26.644959008457</v>
+        <v>-19.42266987697654</v>
       </c>
       <c r="F86">
-        <v>-1.553459075269893</v>
+        <v>1.425625951542261</v>
       </c>
       <c r="G86">
-        <v>-11.92153777440909</v>
+        <v>-9.449405445871781</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-13.09195748192195</v>
       </c>
       <c r="E87">
-        <v>-29.38402679644938</v>
+        <v>-21.48995988638922</v>
       </c>
       <c r="F87">
-        <v>-0.9517147697934709</v>
+        <v>1.489647154635024</v>
       </c>
       <c r="G87">
-        <v>-13.02969442355304</v>
+        <v>-9.134057522828094</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-13.15301365989521</v>
       </c>
       <c r="E88">
-        <v>-27.85041613585451</v>
+        <v>-22.66208749290498</v>
       </c>
       <c r="F88">
-        <v>-1.71238467496659</v>
+        <v>1.536428375340723</v>
       </c>
       <c r="G88">
-        <v>-12.18215404784468</v>
+        <v>-9.157794412650496</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-13.18934341950677</v>
       </c>
       <c r="E89">
-        <v>-30.63275000282329</v>
+        <v>-24.17315867564</v>
       </c>
       <c r="F89">
-        <v>-1.378477230204734</v>
+        <v>1.09144763063969</v>
       </c>
       <c r="G89">
-        <v>-10.8735013517093</v>
+        <v>-9.026313398925145</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-13.20054124255412</v>
       </c>
       <c r="E90">
-        <v>-32.0372227870896</v>
+        <v>-25.80578189421878</v>
       </c>
       <c r="F90">
-        <v>-1.595058029503679</v>
+        <v>1.082975088843857</v>
       </c>
       <c r="G90">
-        <v>-11.85361794849898</v>
+        <v>-9.158206910295892</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-13.17993166179034</v>
       </c>
       <c r="E91">
-        <v>-33.04612503532827</v>
+        <v>-27.18999323703691</v>
       </c>
       <c r="F91">
-        <v>-1.639007062059207</v>
+        <v>0.9717154062390495</v>
       </c>
       <c r="G91">
-        <v>-12.92774223652547</v>
+        <v>-8.770297257459099</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-13.12829044986621</v>
       </c>
       <c r="E92">
-        <v>-35.3619203677564</v>
+        <v>-28.93603027386843</v>
       </c>
       <c r="F92">
-        <v>-1.806247813745204</v>
+        <v>1.065796405644601</v>
       </c>
       <c r="G92">
-        <v>-11.49632449748217</v>
+        <v>-8.989257795571179</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-13.04243323929324</v>
       </c>
       <c r="E93">
-        <v>-34.37911066966596</v>
+        <v>-31.26736069325709</v>
       </c>
       <c r="F93">
-        <v>-1.975723500683955</v>
+        <v>0.7541331107501201</v>
       </c>
       <c r="G93">
-        <v>-11.90752721356088</v>
+        <v>-8.920330222248902</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-12.92331176486986</v>
       </c>
       <c r="E94">
-        <v>-36.46749899260877</v>
+        <v>-32.87230483496155</v>
       </c>
       <c r="F94">
-        <v>-1.938816419419626</v>
+        <v>0.8764564683867175</v>
       </c>
       <c r="G94">
-        <v>-11.60824059124172</v>
+        <v>-9.356911986497821</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-12.77339227967245</v>
       </c>
       <c r="E95">
-        <v>-38.47914012348008</v>
+        <v>-35.47563737043587</v>
       </c>
       <c r="F95">
-        <v>-2.282671728321701</v>
+        <v>0.4303458305482662</v>
       </c>
       <c r="G95">
-        <v>-12.44862099990895</v>
+        <v>-8.969775114059996</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-12.59864091862622</v>
       </c>
       <c r="E96">
-        <v>-40.31066686222188</v>
+        <v>-37.319698500956</v>
       </c>
       <c r="F96">
-        <v>-1.825938935277152</v>
+        <v>0.2193490559115929</v>
       </c>
       <c r="G96">
-        <v>-12.30965367606858</v>
+        <v>-9.765859019249806</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-12.41153821494735</v>
       </c>
       <c r="E97">
-        <v>-43.17518032167503</v>
+        <v>-39.49558045027332</v>
       </c>
       <c r="F97">
-        <v>-2.529103575347929</v>
+        <v>0.02741632868294748</v>
       </c>
       <c r="G97">
-        <v>-11.74490262760814</v>
+        <v>-9.625731219438686</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-12.22242444835232</v>
       </c>
       <c r="E98">
-        <v>-44.0881080860139</v>
+        <v>-42.56999098026632</v>
       </c>
       <c r="F98">
-        <v>-2.02924100510922</v>
+        <v>0.02112322152387964</v>
       </c>
       <c r="G98">
-        <v>-13.17070204429136</v>
+        <v>-9.811331663165522</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-12.04665127929235</v>
       </c>
       <c r="E99">
-        <v>-46.96445300622867</v>
+        <v>-44.41959249469377</v>
       </c>
       <c r="F99">
-        <v>-2.7704293657033</v>
+        <v>-0.377613084548468</v>
       </c>
       <c r="G99">
-        <v>-13.26308193627561</v>
+        <v>-10.01710402497559</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-11.88884379746377</v>
       </c>
       <c r="E100">
-        <v>-48.41286988122015</v>
+        <v>-47.23235694103956</v>
       </c>
       <c r="F100">
-        <v>-2.416361943459513</v>
+        <v>-0.4250743948918657</v>
       </c>
       <c r="G100">
-        <v>-12.5835403642608</v>
+        <v>-10.39377572771994</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-11.76018805378285</v>
       </c>
       <c r="E101">
-        <v>-50.03301996788764</v>
+        <v>-50.38619348440859</v>
       </c>
       <c r="F101">
-        <v>-2.513007568344132</v>
+        <v>-0.5836727894644562</v>
       </c>
       <c r="G101">
-        <v>-13.15853466912448</v>
+        <v>-9.75791974494823</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-11.65891129224424</v>
       </c>
       <c r="E102">
-        <v>-51.26035102103019</v>
+        <v>-52.40901713677199</v>
       </c>
       <c r="F102">
-        <v>-3.343287671476701</v>
+        <v>-0.5668511326158067</v>
       </c>
       <c r="G102">
-        <v>-13.82282818735489</v>
+        <v>-10.71003741137052</v>
       </c>
     </row>
   </sheetData>
